--- a/psdash/demo/weights_table.xlsx
+++ b/psdash/demo/weights_table.xlsx
@@ -500,7 +500,7 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="0"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
